--- a/Klausurplan_2026_2SEM.xlsx
+++ b/Klausurplan_2026_2SEM.xlsx
@@ -1711,7 +1711,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="402">
+  <cellXfs count="403">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3068,6 +3068,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -14299,7 +14303,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="388" t="inlineStr">
+      <c r="F48" s="402" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -14460,7 +14464,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="388" t="inlineStr">
+      <c r="F57" s="402" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
